--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B2" t="n">
         <v>79720</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R2" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B3" t="n">
         <v>79720</v>
@@ -845,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R3" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B2" t="n">
-        <v>79720</v>
+        <v>79723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R2" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B3" t="n">
-        <v>79720</v>
+        <v>79723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R3" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,140 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420439</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79723</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>392</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601344</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6865891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2669</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284474</v>
       </c>
       <c r="B2" t="n">
-        <v>79723</v>
+        <v>79725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123284473</v>
       </c>
       <c r="B3" t="n">
-        <v>79723</v>
+        <v>79725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79723</v>
+        <v>79725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B2" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R2" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B3" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R3" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>79729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R2" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79729</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R3" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
+        <v>79729</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284474</v>
       </c>
       <c r="B2" t="n">
-        <v>79729</v>
+        <v>79735</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123284473</v>
       </c>
       <c r="B3" t="n">
-        <v>79729</v>
+        <v>79735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79729</v>
+        <v>79735</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>79740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R2" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>79740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R3" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79735</v>
+        <v>79740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284473</v>
       </c>
       <c r="B2" t="n">
-        <v>79740</v>
+        <v>79742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123284474</v>
       </c>
       <c r="B3" t="n">
-        <v>79740</v>
+        <v>79742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79740</v>
+        <v>79742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B2" t="n">
         <v>79742</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R2" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B3" t="n">
         <v>79742</v>
@@ -840,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R3" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B2" t="n">
         <v>79742</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R2" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B3" t="n">
         <v>79742</v>
@@ -845,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R3" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284474</v>
+        <v>123284473</v>
       </c>
       <c r="B2" t="n">
-        <v>79742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601336</v>
+        <v>601332</v>
       </c>
       <c r="R2" t="n">
-        <v>6865887</v>
+        <v>6865885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>senvuxen asp</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284473</v>
+        <v>123284474</v>
       </c>
       <c r="B3" t="n">
-        <v>79742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601332</v>
+        <v>601336</v>
       </c>
       <c r="R3" t="n">
-        <v>6865885</v>
+        <v>6865887</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +894,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>senvuxen asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -943,12 +933,7 @@
         <v>123420439</v>
       </c>
       <c r="B4" t="n">
-        <v>79764</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,6 +1048,1516 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123420442</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80305</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601335</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6865895</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_2667</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123420447</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80305</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>392</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601293</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6865887</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_2662</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på senvuxen asp</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123420309</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601079</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6865647</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_2805</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123420315</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601084</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6865651</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_2801</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123420316</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601100</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6865660</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_2800</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123420425</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601406</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6865857</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2024_2682</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123420430</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601383</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6865942</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2024_2676</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123420448</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>601295</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6865880</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024_2661</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123420426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>601460</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6865896</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2024_2680</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123420441</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601354</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6865902</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2024_2668</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123420449</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601292</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6865885</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024_2660</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123420427</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601471</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6865919</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024_2679</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 28822-2024 artfynd.xlsx
+++ b/artfynd/A 28822-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1182,6 +1202,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420442</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1312,6 +1337,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420447</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1437,6 +1467,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420309</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1562,6 +1597,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420315</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1687,6 +1727,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420316</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1812,6 +1857,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1937,6 +1987,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2062,6 +2117,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420448</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2187,6 +2247,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420426</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2312,6 +2377,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420441</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2437,6 +2507,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420449</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2562,8 +2637,30 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420427</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>